--- a/quiz.xlsx
+++ b/quiz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simb/Developer/麻酔quize_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CD4322-332C-1743-B345-1AF3450DCB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34C5A4F-569A-844C-A421-DA7BCECC3D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28380" windowHeight="18620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="28380" windowHeight="18620" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題一覧" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="565">
   <si>
     <t>No.</t>
   </si>
@@ -12240,6 +12240,115 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t xml:space="preserve">チュウシャ </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>筋弛緩薬</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">キンシカンヤク </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>セボフルランの一般的な維持濃度は。</t>
+    <rPh sb="7" eb="10">
+      <t xml:space="preserve">イッパンテキナ </t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t xml:space="preserve">イジ </t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t xml:space="preserve">ノウド </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・1-1.5％程度</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">テイド </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>デスフルランの一般的な維持濃度は。</t>
+    <rPh sb="7" eb="10">
+      <t xml:space="preserve">イッパンテキナ </t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t xml:space="preserve">イジノウド </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・5％前後</t>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">ゼンゴ </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>血圧の一般的な維持目標</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ケツアツノ </t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t xml:space="preserve">イッパンテキナ </t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">イジ </t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t xml:space="preserve">モクヒョウ </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・平均血圧65mmHg以上</t>
+    <rPh sb="1" eb="5">
+      <t xml:space="preserve">ヘイキンケツアツ </t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t xml:space="preserve">イジョウ </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ロクロニウムの一般的な追加タイミング（腹腔鏡手術時のTOF値、それ以外の手術）</t>
+    <rPh sb="7" eb="10">
+      <t xml:space="preserve">イッパンテキナ </t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t xml:space="preserve">ツイカタイミング </t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t xml:space="preserve">フククウキョウ </t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t xml:space="preserve">シュジュツ </t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t xml:space="preserve">ジ </t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t xml:space="preserve">チ </t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t xml:space="preserve">シュジュツデノ </t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・腹腔鏡ではTOF1以下
+・腹腔鏡以外は2以下</t>
+    <rPh sb="1" eb="4">
+      <t xml:space="preserve">フククウキョウ </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t xml:space="preserve">イカ </t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t xml:space="preserve">フククウキョウイガイハ </t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -18595,23 +18704,115 @@
       <c r="A198" s="3">
         <v>197</v>
       </c>
+      <c r="B198" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="F198" s="3">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G198" s="3">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H198" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="I198" s="3"/>
     </row>
     <row r="199" spans="1:9" ht="18">
       <c r="A199" s="3">
         <v>198</v>
       </c>
+      <c r="B199" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F199" s="3">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G199" s="3">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H199" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="I199" s="3"/>
     </row>
-    <row r="200" spans="1:9" ht="18">
+    <row r="200" spans="1:9" ht="30">
       <c r="A200" s="3">
         <v>199</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="F200" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G200" s="3">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="I200" s="3"/>
     </row>
     <row r="201" spans="1:9" ht="18">
       <c r="A201" s="3">
         <v>200</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="F201" s="3">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G201" s="3">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H201" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="I201" s="3"/>
     </row>
@@ -22614,6 +22815,18 @@
         <f>問題一覧!A198</f>
         <v>197</v>
       </c>
+      <c r="B198" s="23" t="str">
+        <f>問題一覧!B198</f>
+        <v>術中維持の基本</v>
+      </c>
+      <c r="C198" s="7" t="str">
+        <f>問題一覧!D198</f>
+        <v>セボフルランの一般的な維持濃度は。</v>
+      </c>
+      <c r="D198" s="23" t="str">
+        <f>問題一覧!G198&amp;"個"</f>
+        <v>1個</v>
+      </c>
       <c r="E198" s="7"/>
       <c r="F198" s="23"/>
     </row>
@@ -22622,6 +22835,18 @@
         <f>問題一覧!A199</f>
         <v>198</v>
       </c>
+      <c r="B199" s="23" t="str">
+        <f>問題一覧!B199</f>
+        <v>術中維持の基本</v>
+      </c>
+      <c r="C199" s="7" t="str">
+        <f>問題一覧!D199</f>
+        <v>血圧の一般的な維持目標</v>
+      </c>
+      <c r="D199" s="23" t="str">
+        <f>問題一覧!G199&amp;"個"</f>
+        <v>1個</v>
+      </c>
       <c r="E199" s="7"/>
       <c r="F199" s="23"/>
     </row>
@@ -22630,6 +22855,18 @@
         <f>問題一覧!A200</f>
         <v>199</v>
       </c>
+      <c r="B200" s="23" t="str">
+        <f>問題一覧!B200</f>
+        <v>術中維持の基本</v>
+      </c>
+      <c r="C200" s="7" t="str">
+        <f>問題一覧!D200</f>
+        <v>ロクロニウムの一般的な追加タイミング（腹腔鏡手術時のTOF値、それ以外の手術）</v>
+      </c>
+      <c r="D200" s="23" t="str">
+        <f>問題一覧!G200&amp;"個"</f>
+        <v>2個</v>
+      </c>
       <c r="E200" s="7"/>
       <c r="F200" s="23"/>
     </row>
@@ -22637,6 +22874,18 @@
       <c r="A201" s="23">
         <f>問題一覧!A201</f>
         <v>200</v>
+      </c>
+      <c r="B201" s="23" t="str">
+        <f>問題一覧!B201</f>
+        <v>術中維持の基本</v>
+      </c>
+      <c r="C201" s="7" t="str">
+        <f>問題一覧!D201</f>
+        <v>デスフルランの一般的な維持濃度は。</v>
+      </c>
+      <c r="D201" s="23" t="str">
+        <f>問題一覧!G201&amp;"個"</f>
+        <v>1個</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="23"/>
@@ -22721,12 +22970,12 @@
         <v>9</v>
       </c>
       <c r="B2" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A2)</f>
-        <v>22</v>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A2)</f>
+        <v>26</v>
       </c>
       <c r="C2" s="26">
         <f t="shared" ref="C2:C11" si="0">IFERROR(B2/$B$11,0)</f>
-        <v>0.1134020618556701</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18">
@@ -22734,12 +22983,12 @@
         <v>57</v>
       </c>
       <c r="B3" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A3)</f>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A3)</f>
         <v>32</v>
       </c>
       <c r="C3" s="26">
         <f t="shared" si="0"/>
-        <v>0.16494845360824742</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18">
@@ -22747,12 +22996,12 @@
         <v>118</v>
       </c>
       <c r="B4" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A4)</f>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A4)</f>
         <v>20</v>
       </c>
       <c r="C4" s="26">
         <f t="shared" si="0"/>
-        <v>0.10309278350515463</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18">
@@ -22760,12 +23009,12 @@
         <v>155</v>
       </c>
       <c r="B5" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A5)</f>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A5)</f>
         <v>38</v>
       </c>
       <c r="C5" s="26">
         <f t="shared" si="0"/>
-        <v>0.19587628865979381</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18">
@@ -22773,12 +23022,12 @@
         <v>255</v>
       </c>
       <c r="B6" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A6)</f>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A6)</f>
         <v>28</v>
       </c>
       <c r="C6" s="26">
         <f t="shared" si="0"/>
-        <v>0.14432989690721648</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18">
@@ -22786,12 +23035,12 @@
         <v>310</v>
       </c>
       <c r="B7" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A7)</f>
-        <v>14</v>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A7)</f>
+        <v>16</v>
       </c>
       <c r="C7" s="26">
         <f t="shared" si="0"/>
-        <v>7.2164948453608241E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18">
@@ -22799,12 +23048,12 @@
         <v>341</v>
       </c>
       <c r="B8" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A8)</f>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A8)</f>
         <v>12</v>
       </c>
       <c r="C8" s="26">
         <f t="shared" si="0"/>
-        <v>6.1855670103092786E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18">
@@ -22812,12 +23061,12 @@
         <v>370</v>
       </c>
       <c r="B9" s="25">
-        <f>COUNTIF(問題一覧!$B$2:$B$195,A9)</f>
+        <f>COUNTIF(問題一覧!$B$2:$B$999,A9)</f>
         <v>13</v>
       </c>
       <c r="C9" s="26">
         <f t="shared" si="0"/>
-        <v>6.7010309278350513E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18">
@@ -22830,7 +23079,7 @@
       </c>
       <c r="C10" s="26">
         <f t="shared" si="0"/>
-        <v>7.7319587628865982E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18">
@@ -22839,7 +23088,7 @@
       </c>
       <c r="B11" s="27">
         <f>SUM(B2:B10)</f>
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C11" s="28">
         <f t="shared" si="0"/>
